--- a/.schema/MHR_SHOKUI.xlsx
+++ b/.schema/MHR_SHOKUI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_fuk\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D1FD91-544F-42F4-83FB-D28D87D4A239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76FF907-5E08-4551-93AF-8F48189B18E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{11E649B2-76F4-47BE-B10D-E666B837FAAF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{11E649B2-76F4-47BE-B10D-E666B837FAAF}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.MHR_SHOKUI" sheetId="2" r:id="rId1"/>
@@ -314,9 +314,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -354,7 +354,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -460,7 +460,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -602,7 +602,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -666,14 +666,14 @@
       <c r="E3" s="3"/>
       <c r="F3" s="5" t="str">
         <f t="shared" ref="F3:F37" ca="1" si="0">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="5" t="str">
         <f t="shared" ref="H3:H37" ca="1" si="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
@@ -693,14 +693,14 @@
       <c r="E4" s="3"/>
       <c r="F4" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
@@ -720,14 +720,14 @@
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
@@ -747,14 +747,14 @@
       <c r="E6" s="3"/>
       <c r="F6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
@@ -774,14 +774,14 @@
       <c r="E7" s="3"/>
       <c r="F7" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
@@ -801,14 +801,14 @@
       <c r="E8" s="3"/>
       <c r="F8" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
@@ -828,14 +828,14 @@
       <c r="E9" s="3"/>
       <c r="F9" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
@@ -855,14 +855,14 @@
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I10" s="2">
         <v>0</v>
@@ -882,14 +882,14 @@
       <c r="E11" s="3"/>
       <c r="F11" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>
@@ -909,14 +909,14 @@
       <c r="E12" s="3"/>
       <c r="F12" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>
@@ -936,14 +936,14 @@
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I13" s="2">
         <v>0</v>
@@ -963,14 +963,14 @@
       <c r="E14" s="3"/>
       <c r="F14" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G14" s="2">
         <v>0</v>
       </c>
       <c r="H14" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I14" s="2">
         <v>0</v>
@@ -990,14 +990,14 @@
       <c r="E15" s="3"/>
       <c r="F15" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
       <c r="H15" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
@@ -1017,14 +1017,14 @@
       <c r="E16" s="3"/>
       <c r="F16" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
       </c>
       <c r="H16" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I16" s="2">
         <v>0</v>
@@ -1044,14 +1044,14 @@
       <c r="E17" s="3"/>
       <c r="F17" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I17" s="2">
         <v>0</v>
@@ -1071,14 +1071,14 @@
       <c r="E18" s="3"/>
       <c r="F18" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
       </c>
       <c r="H18" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I18" s="2">
         <v>0</v>
@@ -1098,14 +1098,14 @@
       <c r="E19" s="3"/>
       <c r="F19" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
       </c>
       <c r="H19" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I19" s="2">
         <v>0</v>
@@ -1125,14 +1125,14 @@
       <c r="E20" s="3"/>
       <c r="F20" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
       </c>
       <c r="H20" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I20" s="2">
         <v>0</v>
@@ -1152,14 +1152,14 @@
       <c r="E21" s="3"/>
       <c r="F21" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
       </c>
       <c r="H21" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I21" s="2">
         <v>0</v>
@@ -1179,14 +1179,14 @@
       <c r="E22" s="3"/>
       <c r="F22" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I22" s="2">
         <v>0</v>
@@ -1206,14 +1206,14 @@
       <c r="E23" s="3"/>
       <c r="F23" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I23" s="2">
         <v>0</v>
@@ -1233,14 +1233,14 @@
       <c r="E24" s="3"/>
       <c r="F24" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
       </c>
       <c r="H24" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I24" s="2">
         <v>0</v>
@@ -1260,14 +1260,14 @@
       <c r="E25" s="3"/>
       <c r="F25" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
       </c>
       <c r="H25" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I25" s="2">
         <v>0</v>
@@ -1287,14 +1287,14 @@
       <c r="E26" s="3"/>
       <c r="F26" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
       </c>
       <c r="H26" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I26" s="2">
         <v>0</v>
@@ -1314,14 +1314,14 @@
       <c r="E27" s="3"/>
       <c r="F27" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I27" s="2">
         <v>0</v>
@@ -1341,14 +1341,14 @@
       <c r="E28" s="3"/>
       <c r="F28" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G28" s="2">
         <v>0</v>
       </c>
       <c r="H28" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I28" s="2">
         <v>0</v>
@@ -1368,14 +1368,14 @@
       <c r="E29" s="4"/>
       <c r="F29" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I29" s="2">
         <v>0</v>
@@ -1395,14 +1395,14 @@
       <c r="E30" s="4"/>
       <c r="F30" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
       </c>
       <c r="H30" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I30" s="2">
         <v>0</v>
@@ -1422,14 +1422,14 @@
       <c r="E31" s="4"/>
       <c r="F31" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
       </c>
       <c r="H31" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I31" s="2">
         <v>0</v>
@@ -1449,14 +1449,14 @@
       <c r="E32" s="4"/>
       <c r="F32" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
       </c>
       <c r="H32" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I32" s="2">
         <v>0</v>
@@ -1476,14 +1476,14 @@
       <c r="E33" s="4"/>
       <c r="F33" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
       </c>
       <c r="H33" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I33" s="2">
         <v>0</v>
@@ -1503,14 +1503,14 @@
       <c r="E34" s="4"/>
       <c r="F34" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G34" s="2">
         <v>0</v>
       </c>
       <c r="H34" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I34" s="2">
         <v>0</v>
@@ -1530,14 +1530,14 @@
       <c r="E35" s="4"/>
       <c r="F35" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G35" s="2">
         <v>0</v>
       </c>
       <c r="H35" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I35" s="2">
         <v>0</v>
@@ -1557,14 +1557,14 @@
       <c r="E36" s="4"/>
       <c r="F36" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I36" s="2">
         <v>0</v>
@@ -1584,14 +1584,14 @@
       <c r="E37" s="4"/>
       <c r="F37" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="G37" s="2">
         <v>0</v>
       </c>
       <c r="H37" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:18:49</v>
+        <v>2026/08/16 10:54:10</v>
       </c>
       <c r="I37" s="2">
         <v>0</v>

--- a/.schema/MHR_SHOKUI.xlsx
+++ b/.schema/MHR_SHOKUI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_fuk\git\sample\.schema\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76FF907-5E08-4551-93AF-8F48189B18E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{11E649B2-76F4-47BE-B10D-E666B837FAAF}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{11E649B2-76F4-47BE-B10D-E666B837FAAF}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.MHR_SHOKUI" sheetId="2" r:id="rId1"/>
@@ -314,9 +314,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -354,7 +354,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -460,7 +460,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -602,7 +602,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -666,14 +666,14 @@
       <c r="E3" s="3"/>
       <c r="F3" s="5" t="str">
         <f t="shared" ref="F3:F37" ca="1" si="0">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="5" t="str">
         <f t="shared" ref="H3:H37" ca="1" si="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
@@ -693,14 +693,14 @@
       <c r="E4" s="3"/>
       <c r="F4" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
@@ -720,14 +720,14 @@
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
@@ -747,14 +747,14 @@
       <c r="E6" s="3"/>
       <c r="F6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
@@ -774,14 +774,14 @@
       <c r="E7" s="3"/>
       <c r="F7" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
@@ -801,14 +801,14 @@
       <c r="E8" s="3"/>
       <c r="F8" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
@@ -828,14 +828,14 @@
       <c r="E9" s="3"/>
       <c r="F9" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
@@ -855,14 +855,14 @@
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I10" s="2">
         <v>0</v>
@@ -882,14 +882,14 @@
       <c r="E11" s="3"/>
       <c r="F11" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>
@@ -909,14 +909,14 @@
       <c r="E12" s="3"/>
       <c r="F12" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>
@@ -936,14 +936,14 @@
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I13" s="2">
         <v>0</v>
@@ -963,14 +963,14 @@
       <c r="E14" s="3"/>
       <c r="F14" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G14" s="2">
         <v>0</v>
       </c>
       <c r="H14" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I14" s="2">
         <v>0</v>
@@ -990,14 +990,14 @@
       <c r="E15" s="3"/>
       <c r="F15" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
       <c r="H15" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
@@ -1017,14 +1017,14 @@
       <c r="E16" s="3"/>
       <c r="F16" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
       </c>
       <c r="H16" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I16" s="2">
         <v>0</v>
@@ -1044,14 +1044,14 @@
       <c r="E17" s="3"/>
       <c r="F17" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I17" s="2">
         <v>0</v>
@@ -1071,14 +1071,14 @@
       <c r="E18" s="3"/>
       <c r="F18" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
       </c>
       <c r="H18" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I18" s="2">
         <v>0</v>
@@ -1098,14 +1098,14 @@
       <c r="E19" s="3"/>
       <c r="F19" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
       </c>
       <c r="H19" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I19" s="2">
         <v>0</v>
@@ -1125,14 +1125,14 @@
       <c r="E20" s="3"/>
       <c r="F20" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
       </c>
       <c r="H20" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I20" s="2">
         <v>0</v>
@@ -1152,14 +1152,14 @@
       <c r="E21" s="3"/>
       <c r="F21" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
       </c>
       <c r="H21" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I21" s="2">
         <v>0</v>
@@ -1179,14 +1179,14 @@
       <c r="E22" s="3"/>
       <c r="F22" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I22" s="2">
         <v>0</v>
@@ -1206,14 +1206,14 @@
       <c r="E23" s="3"/>
       <c r="F23" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I23" s="2">
         <v>0</v>
@@ -1233,14 +1233,14 @@
       <c r="E24" s="3"/>
       <c r="F24" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
       </c>
       <c r="H24" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I24" s="2">
         <v>0</v>
@@ -1260,14 +1260,14 @@
       <c r="E25" s="3"/>
       <c r="F25" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
       </c>
       <c r="H25" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I25" s="2">
         <v>0</v>
@@ -1287,14 +1287,14 @@
       <c r="E26" s="3"/>
       <c r="F26" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
       </c>
       <c r="H26" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I26" s="2">
         <v>0</v>
@@ -1314,14 +1314,14 @@
       <c r="E27" s="3"/>
       <c r="F27" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I27" s="2">
         <v>0</v>
@@ -1341,14 +1341,14 @@
       <c r="E28" s="3"/>
       <c r="F28" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G28" s="2">
         <v>0</v>
       </c>
       <c r="H28" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I28" s="2">
         <v>0</v>
@@ -1368,14 +1368,14 @@
       <c r="E29" s="4"/>
       <c r="F29" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I29" s="2">
         <v>0</v>
@@ -1395,14 +1395,14 @@
       <c r="E30" s="4"/>
       <c r="F30" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
       </c>
       <c r="H30" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I30" s="2">
         <v>0</v>
@@ -1422,14 +1422,14 @@
       <c r="E31" s="4"/>
       <c r="F31" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
       </c>
       <c r="H31" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I31" s="2">
         <v>0</v>
@@ -1449,14 +1449,14 @@
       <c r="E32" s="4"/>
       <c r="F32" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
       </c>
       <c r="H32" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I32" s="2">
         <v>0</v>
@@ -1476,14 +1476,14 @@
       <c r="E33" s="4"/>
       <c r="F33" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
       </c>
       <c r="H33" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I33" s="2">
         <v>0</v>
@@ -1503,14 +1503,14 @@
       <c r="E34" s="4"/>
       <c r="F34" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G34" s="2">
         <v>0</v>
       </c>
       <c r="H34" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I34" s="2">
         <v>0</v>
@@ -1530,14 +1530,14 @@
       <c r="E35" s="4"/>
       <c r="F35" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G35" s="2">
         <v>0</v>
       </c>
       <c r="H35" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I35" s="2">
         <v>0</v>
@@ -1557,14 +1557,14 @@
       <c r="E36" s="4"/>
       <c r="F36" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I36" s="2">
         <v>0</v>
@@ -1584,14 +1584,14 @@
       <c r="E37" s="4"/>
       <c r="F37" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="G37" s="2">
         <v>0</v>
       </c>
       <c r="H37" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:54:10</v>
+        <v>2026/09/01 15:08:32</v>
       </c>
       <c r="I37" s="2">
         <v>0</v>
